--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FA8B91-DEB7-4800-A4FC-4C902C381B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39579C87-1193-4118-B5B6-F1EAEF2948D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="4185" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="22">
   <si>
     <t>CPU</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>gpu</t>
-  </si>
-  <si>
-    <t>check</t>
   </si>
   <si>
     <t>mem_gb_per_cpu</t>
@@ -352,17 +349,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,12 +421,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC099051-1441-4E77-BD0B-262A4DC004A8}" name="Table1" displayName="Table1" ref="A1:L39" totalsRowShown="0">
-  <autoFilter ref="A1:L39" xr:uid="{BC099051-1441-4E77-BD0B-262A4DC004A8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L39">
-    <sortCondition ref="C1:C39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC099051-1441-4E77-BD0B-262A4DC004A8}" name="Table1" displayName="Table1" ref="A1:K37" totalsRowShown="0">
+  <autoFilter ref="A1:K37" xr:uid="{BC099051-1441-4E77-BD0B-262A4DC004A8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
+    <sortCondition ref="K1:K37"/>
   </sortState>
-  <tableColumns count="12">
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{941974C2-F053-42C8-B3FA-394C3B11320A}" name="hardware_utilization_strategy"/>
     <tableColumn id="2" xr3:uid="{EA696286-CA35-4B79-96BE-D9166FEB1610}" name="device"/>
     <tableColumn id="3" xr3:uid="{B8BF4F7E-AF93-4396-BCCB-447D83456B0B}" name="run_mode"/>
@@ -446,9 +443,6 @@
     </tableColumn>
     <tableColumn id="12" xr3:uid="{EE4B90D1-D246-40CB-846F-A616F43A9F0E}" name="devices_per_node">
       <calculatedColumnFormula>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" xr3:uid="{69C8AF60-3FAA-4DC7-9793-60E51764A88E}" name="check">
-      <calculatedColumnFormula>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -718,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -731,10 +725,9 @@
     <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -757,7 +750,7 @@
         <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>9</v>
@@ -768,11 +761,8 @@
       <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -809,54 +799,46 @@
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
         <v>1</v>
       </c>
-      <c r="L2" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>1</v>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>0</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" s="10">
         <v>1</v>
       </c>
       <c r="E3" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="10">
         <v>1</v>
       </c>
       <c r="G3" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>2</v>
-      </c>
-      <c r="L3" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
@@ -870,119 +852,107 @@
         <v>1</v>
       </c>
       <c r="E4" s="10">
+        <v>2</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <v>2</v>
+      </c>
+      <c r="H4" s="11">
+        <v>8</v>
+      </c>
+      <c r="I4" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>2</v>
+      </c>
+      <c r="J4" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>2</v>
+      </c>
+      <c r="K4" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
+        <v>2</v>
+      </c>
+      <c r="I5" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>2</v>
+      </c>
+      <c r="J5" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>2</v>
+      </c>
+      <c r="K5" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="10">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10">
-        <v>3</v>
-      </c>
-      <c r="H4" s="11">
-        <v>8</v>
-      </c>
-      <c r="I4" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>3</v>
-      </c>
-      <c r="J4" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>3</v>
-      </c>
-      <c r="K4" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>3</v>
-      </c>
-      <c r="L4" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10">
-        <v>4</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10">
-        <v>4</v>
-      </c>
-      <c r="H5" s="11">
-        <v>8</v>
-      </c>
-      <c r="I5" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>4</v>
-      </c>
-      <c r="J5" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>4</v>
-      </c>
-      <c r="K5" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>4</v>
-      </c>
-      <c r="L5" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>1</v>
+      <c r="B6" s="15" t="s">
+        <v>0</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="10">
         <v>1</v>
       </c>
       <c r="E6" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" s="11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>5</v>
-      </c>
-      <c r="L6" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
@@ -996,35 +966,31 @@
         <v>1</v>
       </c>
       <c r="E7" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10">
         <v>1</v>
       </c>
       <c r="G7" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H7" s="11">
         <v>8</v>
       </c>
       <c r="I7" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J7" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="13">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>6</v>
-      </c>
-      <c r="L7" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
@@ -1038,352 +1004,320 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
+        <v>4</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>4</v>
+      </c>
+      <c r="H8" s="11">
+        <v>8</v>
+      </c>
+      <c r="I8" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>4</v>
+      </c>
+      <c r="J8" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>4</v>
+      </c>
+      <c r="K8" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>2</v>
+      </c>
+      <c r="I9" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>4</v>
+      </c>
+      <c r="J9" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>4</v>
+      </c>
+      <c r="K9" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>2</v>
+      </c>
+      <c r="I10" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>4</v>
+      </c>
+      <c r="J10" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>4</v>
+      </c>
+      <c r="K10" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>4</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>4</v>
+      </c>
+      <c r="J11" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>4</v>
+      </c>
+      <c r="K11" s="13">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="16">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>5</v>
+      </c>
+      <c r="F12" s="16">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10">
+        <v>5</v>
+      </c>
+      <c r="H12" s="11">
+        <v>8</v>
+      </c>
+      <c r="I12" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>5</v>
+      </c>
+      <c r="J12" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>5</v>
+      </c>
+      <c r="K12" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>6</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11">
+        <v>8</v>
+      </c>
+      <c r="I13" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>6</v>
+      </c>
+      <c r="J13" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>6</v>
+      </c>
+      <c r="K13" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10">
         <v>7</v>
       </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="F14" s="10">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10">
         <v>7</v>
       </c>
-      <c r="H8" s="11">
-        <v>8</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H14" s="11">
+        <v>8</v>
+      </c>
+      <c r="I14" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
         <v>7</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J14" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
         <v>7</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K14" s="17">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
         <v>7</v>
       </c>
-      <c r="L8" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="10">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10">
-        <v>8</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1</v>
-      </c>
-      <c r="G9" s="10">
-        <v>8</v>
-      </c>
-      <c r="H9" s="11">
-        <v>8</v>
-      </c>
-      <c r="I9" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J9" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K9" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L9" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10">
+        <v>8</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10">
+        <v>8</v>
+      </c>
+      <c r="H15" s="11">
+        <v>8</v>
+      </c>
+      <c r="I15" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>8</v>
+      </c>
+      <c r="J15" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>8</v>
+      </c>
+      <c r="K15" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="10">
-        <v>2</v>
-      </c>
-      <c r="E10" s="10">
-        <v>16</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10">
-        <v>16</v>
-      </c>
-      <c r="H10" s="11">
-        <v>8</v>
-      </c>
-      <c r="I10" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J10" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K10" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L10" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>2</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11">
-        <v>2</v>
-      </c>
-      <c r="I11" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>4</v>
-      </c>
-      <c r="J11" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>4</v>
-      </c>
-      <c r="K11" s="13">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>4</v>
-      </c>
-      <c r="L11" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="18">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10">
-        <v>2</v>
-      </c>
-      <c r="F12" s="18">
-        <v>4</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <v>2</v>
-      </c>
-      <c r="I12" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J12" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K12" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L12" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="10">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10">
-        <v>4</v>
-      </c>
-      <c r="F13" s="10">
-        <v>2</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
-        <v>2</v>
-      </c>
-      <c r="I13" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J13" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K13" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L13" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="10">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10">
-        <v>2</v>
-      </c>
-      <c r="F14" s="10">
-        <v>8</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2</v>
-      </c>
-      <c r="I14" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J14" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K14" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L14" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10">
-        <v>4</v>
-      </c>
-      <c r="F15" s="10">
-        <v>4</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
-        <v>2</v>
-      </c>
-      <c r="I15" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J15" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K15" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L15" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="D16" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F16" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H16" s="11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I16" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
@@ -1393,16 +1327,12 @@
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
         <v>16</v>
       </c>
-      <c r="K16" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L16" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K16" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>5</v>
       </c>
@@ -1419,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="10">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G17" s="10">
         <v>0</v>
@@ -1429,22 +1359,18 @@
       </c>
       <c r="I17" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J17" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K17" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L17" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="K17" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
@@ -1461,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G18" s="10">
         <v>0</v>
@@ -1471,30 +1397,26 @@
       </c>
       <c r="I18" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J18" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K18" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L18" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="K18" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
@@ -1503,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="10">
         <v>0</v>
@@ -1513,39 +1435,35 @@
       </c>
       <c r="I19" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J19" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K19" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L19" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="K19" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" s="10">
         <v>1</v>
       </c>
       <c r="E20" s="10">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F20" s="10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G20" s="10">
         <v>0</v>
@@ -1555,22 +1473,18 @@
       </c>
       <c r="I20" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J20" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K20" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L20" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="K20" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>5</v>
       </c>
@@ -1587,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="10">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G21" s="10">
         <v>0</v>
@@ -1597,22 +1511,18 @@
       </c>
       <c r="I21" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J21" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K21" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L21" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K21" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>5</v>
       </c>
@@ -1629,7 +1539,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="10">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G22" s="10">
         <v>0</v>
@@ -1639,22 +1549,18 @@
       </c>
       <c r="I22" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J22" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K22" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L22" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K22" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>5</v>
       </c>
@@ -1671,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="F23" s="10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G23" s="10">
         <v>0</v>
@@ -1681,30 +1587,26 @@
       </c>
       <c r="I23" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J23" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K23" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L23" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K23" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
@@ -1713,7 +1615,7 @@
         <v>16</v>
       </c>
       <c r="F24" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="10">
         <v>0</v>
@@ -1723,39 +1625,35 @@
       </c>
       <c r="I24" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="J24" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K24" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L24" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K24" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="10">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G25" s="10">
         <v>0</v>
@@ -1765,22 +1663,18 @@
       </c>
       <c r="I25" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="J25" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>128</v>
-      </c>
-      <c r="K25" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L25" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K25" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>5</v>
       </c>
@@ -1791,38 +1685,34 @@
         <v>17</v>
       </c>
       <c r="D26" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" s="10">
+        <v>16</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>2</v>
+      </c>
+      <c r="I26" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
         <v>32</v>
       </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11">
-        <v>2</v>
-      </c>
-      <c r="I26" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>128</v>
-      </c>
       <c r="J26" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>128</v>
-      </c>
-      <c r="K26" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L26" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="K26" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>5</v>
       </c>
@@ -1833,13 +1723,13 @@
         <v>17</v>
       </c>
       <c r="D27" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G27" s="10">
         <v>0</v>
@@ -1849,22 +1739,18 @@
       </c>
       <c r="I27" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>128</v>
-      </c>
-      <c r="K27" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L27" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="K27" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>5</v>
       </c>
@@ -1875,13 +1761,13 @@
         <v>17</v>
       </c>
       <c r="D28" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F28" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G28" s="10">
         <v>0</v>
@@ -1891,375 +1777,339 @@
       </c>
       <c r="I28" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>32</v>
+      </c>
+      <c r="J28" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>32</v>
+      </c>
+      <c r="K28" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1</v>
+      </c>
+      <c r="E29" s="10">
+        <v>16</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11">
+        <v>2</v>
+      </c>
+      <c r="I29" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>32</v>
+      </c>
+      <c r="J29" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>32</v>
+      </c>
+      <c r="K29" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>32</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11">
+        <v>2</v>
+      </c>
+      <c r="I30" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>32</v>
+      </c>
+      <c r="J30" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>32</v>
+      </c>
+      <c r="K30" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="10">
+        <v>2</v>
+      </c>
+      <c r="E31" s="10">
+        <v>2</v>
+      </c>
+      <c r="F31" s="10">
+        <v>32</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>2</v>
+      </c>
+      <c r="I31" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>64</v>
+      </c>
+      <c r="J31" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>64</v>
+      </c>
+      <c r="K31" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="10">
+        <v>2</v>
+      </c>
+      <c r="E32" s="10">
+        <v>4</v>
+      </c>
+      <c r="F32" s="10">
+        <v>16</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11">
+        <v>2</v>
+      </c>
+      <c r="I32" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>64</v>
+      </c>
+      <c r="J32" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>64</v>
+      </c>
+      <c r="K32" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="10">
+        <v>2</v>
+      </c>
+      <c r="E33" s="10">
+        <v>8</v>
+      </c>
+      <c r="F33" s="10">
+        <v>8</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <v>2</v>
+      </c>
+      <c r="I33" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>64</v>
+      </c>
+      <c r="J33" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>64</v>
+      </c>
+      <c r="K33" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10">
+        <v>16</v>
+      </c>
+      <c r="F34" s="10">
+        <v>4</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <v>2</v>
+      </c>
+      <c r="I34" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>64</v>
+      </c>
+      <c r="J34" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>64</v>
+      </c>
+      <c r="K34" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="10">
+        <v>3</v>
+      </c>
+      <c r="E35" s="10">
+        <v>4</v>
+      </c>
+      <c r="F35" s="10">
+        <v>32</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <v>2</v>
+      </c>
+      <c r="I35" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
         <v>128</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J35" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
         <v>128</v>
       </c>
-      <c r="K28" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L28" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="10">
-        <v>1</v>
-      </c>
-      <c r="E29" s="10">
-        <v>2</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11">
-        <v>2</v>
-      </c>
-      <c r="I29" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>2</v>
-      </c>
-      <c r="J29" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>2</v>
-      </c>
-      <c r="K29" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>2</v>
-      </c>
-      <c r="L29" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="10">
-        <v>1</v>
-      </c>
-      <c r="E30" s="10">
-        <v>4</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0</v>
-      </c>
-      <c r="H30" s="11">
-        <v>2</v>
-      </c>
-      <c r="I30" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>4</v>
-      </c>
-      <c r="J30" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>4</v>
-      </c>
-      <c r="K30" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>4</v>
-      </c>
-      <c r="L30" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="10">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10">
-        <v>8</v>
-      </c>
-      <c r="F31" s="10">
-        <v>1</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0</v>
-      </c>
-      <c r="H31" s="11">
-        <v>2</v>
-      </c>
-      <c r="I31" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J31" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K31" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L31" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="10">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10">
-        <v>16</v>
-      </c>
-      <c r="F32" s="10">
-        <v>1</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0</v>
-      </c>
-      <c r="H32" s="11">
-        <v>2</v>
-      </c>
-      <c r="I32" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J32" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K32" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L32" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="K35" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>42.666666666666664</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="10">
         <v>3</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="10">
-        <v>1</v>
-      </c>
-      <c r="E33" s="10">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10">
-        <v>2</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0</v>
-      </c>
-      <c r="H33" s="11">
-        <v>2</v>
-      </c>
-      <c r="I33" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>2</v>
-      </c>
-      <c r="J33" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>2</v>
-      </c>
-      <c r="K33" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>2</v>
-      </c>
-      <c r="L33" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="E36" s="10">
+        <v>8</v>
+      </c>
+      <c r="F36" s="10">
+        <v>16</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <v>2</v>
+      </c>
+      <c r="I36" s="12">
+        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
+        <v>128</v>
+      </c>
+      <c r="J36" s="12">
+        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
+        <v>128</v>
+      </c>
+      <c r="K36" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>42.666666666666664</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="10">
         <v>3</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="10">
-        <v>1</v>
-      </c>
-      <c r="E34" s="10">
-        <v>1</v>
-      </c>
-      <c r="F34" s="10">
-        <v>4</v>
-      </c>
-      <c r="G34" s="10">
-        <v>0</v>
-      </c>
-      <c r="H34" s="11">
-        <v>2</v>
-      </c>
-      <c r="I34" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>4</v>
-      </c>
-      <c r="J34" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>4</v>
-      </c>
-      <c r="K34" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>4</v>
-      </c>
-      <c r="L34" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1</v>
-      </c>
-      <c r="E35" s="10">
-        <v>1</v>
-      </c>
-      <c r="F35" s="10">
-        <v>8</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0</v>
-      </c>
-      <c r="H35" s="11">
-        <v>2</v>
-      </c>
-      <c r="I35" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J35" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K35" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L35" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="10">
-        <v>1</v>
-      </c>
-      <c r="E36" s="10">
-        <v>1</v>
-      </c>
-      <c r="F36" s="10">
-        <v>16</v>
-      </c>
-      <c r="G36" s="10">
-        <v>0</v>
-      </c>
-      <c r="H36" s="11">
-        <v>2</v>
-      </c>
-      <c r="I36" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J36" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K36" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L36" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="10">
-        <v>1</v>
-      </c>
       <c r="E37" s="10">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F37" s="10">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G37" s="10">
         <v>0</v>
@@ -2269,103 +2119,15 @@
       </c>
       <c r="I37" s="12">
         <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="J37" s="12">
         <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K37" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L37" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="10">
-        <v>1</v>
-      </c>
-      <c r="E38" s="10">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10">
-        <v>64</v>
-      </c>
-      <c r="G38" s="10">
-        <v>0</v>
-      </c>
-      <c r="H38" s="11">
-        <v>2</v>
-      </c>
-      <c r="I38" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>64</v>
-      </c>
-      <c r="J38" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K38" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L38" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="10">
-        <v>1</v>
-      </c>
-      <c r="E39" s="10">
-        <v>1</v>
-      </c>
-      <c r="F39" s="10">
-        <v>1</v>
-      </c>
-      <c r="G39" s="10">
-        <v>0</v>
-      </c>
-      <c r="H39" s="11">
-        <v>2</v>
-      </c>
-      <c r="I39" s="12">
-        <f>Table1[[#This Row], [n_mpi_procs]]*Table1[[#This Row], [n_omp_threads]]</f>
-        <v>1</v>
-      </c>
-      <c r="J39" s="12">
-        <f>Table1[[#This Row], [n_omp_threads]]*Table1[[#This Row], [n_mpi_procs]]</f>
-        <v>1</v>
-      </c>
-      <c r="K39" s="19">
-        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
-      </c>
-      <c r="L39" t="b">
-        <f>Table1[[#This Row], [n_mpi_procs]]&gt;=Table1[[#This Row], [n_nodes]]</f>
-        <v>1</v>
+        <v>128</v>
+      </c>
+      <c r="K37" s="17">
+        <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
+        <v>42.666666666666664</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39579C87-1193-4118-B5B6-F1EAEF2948D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE793E4-EE03-4410-9199-BC92D0B0BAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="4185" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -2027,7 +2027,7 @@
         <v>17</v>
       </c>
       <c r="D35" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="10">
         <v>4</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K35" s="17">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>42.666666666666664</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2065,7 +2065,7 @@
         <v>17</v>
       </c>
       <c r="D36" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="10">
         <v>8</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K36" s="17">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>42.666666666666664</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2103,7 +2103,7 @@
         <v>17</v>
       </c>
       <c r="D37" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="10">
         <v>16</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="K37" s="17">
         <f>Table1[[#This Row], [total_devices]]/Table1[[#This Row], [n_nodes]]</f>
-        <v>42.666666666666664</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_frontier.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -709,12 +709,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>system.gpu_hardware</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>system.gpu_compilation_backend</t>
+          <t>analysis.hpc_ensemble_partition</t>
         </is>
       </c>
     </row>
@@ -742,6 +737,11 @@
       <c r="G2" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -767,6 +767,11 @@
       <c r="G3" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -791,6 +796,11 @@
       </c>
       <c r="G4" s="11" t="n">
         <v>8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -817,6 +827,11 @@
       <c r="G5" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -842,6 +857,11 @@
       <c r="G6" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -867,6 +887,11 @@
       <c r="G7" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +917,11 @@
       <c r="G8" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -917,6 +947,11 @@
       <c r="G9" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -941,6 +976,11 @@
       </c>
       <c r="G10" s="11" t="n">
         <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -967,6 +1007,11 @@
       <c r="G11" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -992,6 +1037,11 @@
       <c r="G12" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1017,6 +1067,11 @@
       <c r="G13" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1042,6 +1097,11 @@
       <c r="G14" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1067,6 +1127,11 @@
       <c r="G15" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1092,6 +1157,11 @@
       <c r="G16" s="11" t="n">
         <v>8</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1117,6 +1187,11 @@
       <c r="G17" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1142,6 +1217,11 @@
       <c r="G18" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1167,6 +1247,11 @@
       <c r="G19" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1192,6 +1277,11 @@
       <c r="G20" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1217,6 +1307,11 @@
       <c r="G21" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1242,6 +1337,11 @@
       <c r="G22" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1267,6 +1367,11 @@
       <c r="G23" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1292,6 +1397,11 @@
       <c r="G24" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1317,6 +1427,11 @@
       <c r="G25" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1342,6 +1457,11 @@
       <c r="G26" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1367,6 +1487,11 @@
       <c r="G27" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1392,6 +1517,11 @@
       <c r="G28" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1417,6 +1547,11 @@
       <c r="G29" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1442,6 +1577,11 @@
       <c r="G30" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1467,6 +1607,11 @@
       <c r="G31" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1492,6 +1637,11 @@
       <c r="G32" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1517,6 +1667,11 @@
       <c r="G33" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1542,6 +1697,11 @@
       <c r="G34" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1567,6 +1727,11 @@
       <c r="G35" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1592,6 +1757,11 @@
       <c r="G36" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1617,6 +1787,11 @@
       <c r="G37" s="11" t="n">
         <v>2</v>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1645,9 +1820,9 @@
       <c r="H38" t="n">
         <v>1.1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1678,9 +1853,9 @@
       <c r="H39" t="n">
         <v>1.1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1711,9 +1886,9 @@
       <c r="H40" t="n">
         <v>1.1</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1744,9 +1919,9 @@
       <c r="H41" t="n">
         <v>1.1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1777,9 +1952,9 @@
       <c r="H42" t="n">
         <v>1.1</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1810,9 +1985,9 @@
       <c r="H43" t="n">
         <v>0.35</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1843,9 +2018,9 @@
       <c r="H44" t="n">
         <v>0.35</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1876,9 +2051,9 @@
       <c r="H45" t="n">
         <v>0.35</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1909,9 +2084,9 @@
       <c r="H46" t="n">
         <v>0.35</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -1942,9 +2117,9 @@
       <c r="H47" t="n">
         <v>0.35</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>HIP</t>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>batch</t>
         </is>
       </c>
     </row>
